--- a/Notebooks/FRB_Kritti.xlsx
+++ b/Notebooks/FRB_Kritti.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Research\FRB\cosmology\FRB_GW_association_cosmo\Notebooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A735A897-7A43-49E2-927E-8D110FA92037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA58656-6580-496F-89DF-FC0671B858CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
   <si>
     <t>FRB</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -159,10 +159,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20221418A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>20221029A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -207,10 +203,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>01:55:46.96</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>21:30:18.03</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -408,6 +400,18 @@
   </si>
   <si>
     <t>20230124A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20220418A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04:55:46.96</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DM_ext_plot</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -415,7 +419,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,13 +434,27 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -451,9 +469,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -734,15 +754,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.9140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="6.58203125" customWidth="1"/>
+    <col min="5" max="5" width="6.5" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -756,614 +779,711 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2">
+        <v>0.4012</v>
+      </c>
+      <c r="E2">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F2" s="3">
+        <v>559.42999999999995</v>
+      </c>
+      <c r="G2">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3">
+        <v>4.3299999999999998E-2</v>
+      </c>
+      <c r="E3">
+        <v>1E-4</v>
+      </c>
+      <c r="F3" s="3">
+        <v>182.98</v>
+      </c>
+      <c r="G3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="E4">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F4" s="3">
+        <v>346.65</v>
+      </c>
+      <c r="G4">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5">
+        <v>0.24179999999999999</v>
+      </c>
+      <c r="E5">
+        <v>1E-4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>363.43</v>
+      </c>
+      <c r="G5">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D6">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="E6">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F6" s="3">
+        <v>416.71</v>
+      </c>
+      <c r="G6">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7">
+        <v>1.12E-2</v>
+      </c>
+      <c r="E7">
+        <v>1E-4</v>
+      </c>
+      <c r="F7" s="3">
+        <v>-22.31</v>
+      </c>
+      <c r="G7">
+        <v>-22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8">
+        <v>0.37140000000000001</v>
+      </c>
+      <c r="E8">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F8" s="3">
+        <v>428.75</v>
+      </c>
+      <c r="G8">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2">
-        <v>1.12E-2</v>
-      </c>
-      <c r="E2">
-        <v>1E-4</v>
-      </c>
-      <c r="F2">
-        <v>-22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9">
+        <v>0.62139999999999995</v>
+      </c>
+      <c r="E9">
+        <v>1E-4</v>
+      </c>
+      <c r="F9" s="3">
+        <v>585.84</v>
+      </c>
+      <c r="G9">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10">
+        <v>0.3</v>
+      </c>
+      <c r="E10">
+        <v>1E-4</v>
+      </c>
+      <c r="F10" s="3">
+        <v>307.81</v>
+      </c>
+      <c r="G10">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D3">
-        <v>3.6799999999999999E-2</v>
-      </c>
-      <c r="E3">
-        <v>1E-4</v>
-      </c>
-      <c r="F3">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4">
-        <v>4.3299999999999998E-2</v>
-      </c>
-      <c r="E4">
-        <v>1E-4</v>
-      </c>
-      <c r="F4">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5">
+      <c r="D11">
         <v>8.9399999999999993E-2</v>
       </c>
-      <c r="E5">
-        <v>1E-4</v>
-      </c>
-      <c r="F5">
+      <c r="E11">
+        <v>1E-4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>214.29</v>
+      </c>
+      <c r="G11">
         <v>214</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D6">
-        <v>9.3899999999999997E-2</v>
-      </c>
-      <c r="E6">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="F6">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D7">
-        <v>0.1139</v>
-      </c>
-      <c r="E7">
-        <v>1E-4</v>
-      </c>
-      <c r="F7">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8">
-        <v>0.127</v>
-      </c>
-      <c r="E8">
-        <v>1E-4</v>
-      </c>
-      <c r="F8">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9">
-        <v>0.15820000000000001</v>
-      </c>
-      <c r="E9">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="F9">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10">
-        <v>0.23949999999999999</v>
-      </c>
-      <c r="E10">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="F10">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12">
+        <v>0.3619</v>
+      </c>
+      <c r="E12">
+        <v>4.0000000000000002E-4</v>
+      </c>
+      <c r="F12" s="3">
+        <v>601.37</v>
+      </c>
+      <c r="G12">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11">
-        <v>0.2414</v>
-      </c>
-      <c r="E11">
-        <v>1E-4</v>
-      </c>
-      <c r="F11">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12">
-        <v>0.24179999999999999</v>
-      </c>
-      <c r="E12">
-        <v>1E-4</v>
-      </c>
-      <c r="F12">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D13">
+        <v>0.2414</v>
+      </c>
+      <c r="E13">
+        <v>1E-4</v>
+      </c>
+      <c r="F13" s="3">
+        <v>571.5</v>
+      </c>
+      <c r="G13">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14">
+        <v>0.1139</v>
+      </c>
+      <c r="E14">
+        <v>1E-4</v>
+      </c>
+      <c r="F14" s="3">
+        <v>575.86</v>
+      </c>
+      <c r="G14">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15">
+        <v>0.15820000000000001</v>
+      </c>
+      <c r="E15">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F15" s="3">
+        <v>274.68</v>
+      </c>
+      <c r="G15">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16">
+        <v>0.28470000000000001</v>
+      </c>
+      <c r="E16">
+        <v>1E-4</v>
+      </c>
+      <c r="F16" s="3">
+        <v>387.85</v>
+      </c>
+      <c r="G16">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17">
+        <v>0.54220000000000002</v>
+      </c>
+      <c r="E17">
+        <v>2.9999999999999997E-4</v>
+      </c>
+      <c r="F17" s="3">
+        <v>405.36</v>
+      </c>
+      <c r="G17">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="E18">
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1347.42</v>
+      </c>
+      <c r="G18">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19">
+        <v>0.23949999999999999</v>
+      </c>
+      <c r="E19">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="F19" s="3">
+        <v>366.21100000000001</v>
+      </c>
+      <c r="G19">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20">
         <v>0.2505</v>
       </c>
-      <c r="E13">
-        <v>1E-4</v>
-      </c>
-      <c r="F13">
+      <c r="E20">
+        <v>1E-4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>323.5</v>
+      </c>
+      <c r="G20">
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="1" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D14">
-        <v>0.2621</v>
-      </c>
-      <c r="E14">
-        <v>1E-4</v>
-      </c>
-      <c r="F14">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15">
-        <v>0.27060000000000001</v>
-      </c>
-      <c r="E15">
-        <v>1E-4</v>
-      </c>
-      <c r="F15">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16">
+      <c r="D21">
         <v>0.27639999999999998</v>
       </c>
-      <c r="E16">
+      <c r="E21">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="F16">
+      <c r="F21" s="3">
+        <v>496.8</v>
+      </c>
+      <c r="G21">
         <v>496</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17">
-        <v>0.28470000000000001</v>
-      </c>
-      <c r="E17">
-        <v>1E-4</v>
-      </c>
-      <c r="F17">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18">
-        <v>0.3</v>
-      </c>
-      <c r="E18">
-        <v>1E-4</v>
-      </c>
-      <c r="F18">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D19">
-        <v>0.30149999999999999</v>
-      </c>
-      <c r="E19">
-        <v>1.1000000000000001E-3</v>
-      </c>
-      <c r="F19">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20">
-        <v>0.32700000000000001</v>
-      </c>
-      <c r="E20">
-        <v>1E-4</v>
-      </c>
-      <c r="F20">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="E21">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="F21">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="D22">
-        <v>0.3619</v>
+        <v>0.55300000000000005</v>
       </c>
       <c r="E22">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F22">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="F22" s="3">
+        <v>662.3</v>
+      </c>
+      <c r="G22">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D23">
-        <v>0.37140000000000001</v>
+        <v>9.3899999999999997E-2</v>
       </c>
       <c r="E23">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="F23">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F23" s="3">
+        <v>551.1</v>
+      </c>
+      <c r="G23">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D24">
-        <v>0.4012</v>
+        <v>0.53100000000000003</v>
       </c>
       <c r="E24">
         <v>2.9999999999999997E-4</v>
       </c>
-      <c r="F24">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F24" s="3">
+        <v>788.8</v>
+      </c>
+      <c r="G24">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25">
+        <v>0.27060000000000001</v>
+      </c>
+      <c r="E25">
+        <v>1E-4</v>
+      </c>
+      <c r="F25" s="3">
+        <v>580.65</v>
+      </c>
+      <c r="G25">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26">
+        <v>0.30149999999999999</v>
+      </c>
+      <c r="E26">
+        <v>1.1000000000000001E-3</v>
+      </c>
+      <c r="F26" s="3">
+        <v>413</v>
+      </c>
+      <c r="G26">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D27">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="E27">
+        <v>1E-4</v>
+      </c>
+      <c r="F27" s="3">
+        <v>411.9</v>
+      </c>
+      <c r="G27">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28">
+        <v>0.127</v>
+      </c>
+      <c r="E28">
+        <v>1E-4</v>
+      </c>
+      <c r="F28" s="3">
+        <v>306.35000000000002</v>
+      </c>
+      <c r="G28">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25">
+      <c r="B29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29">
         <v>0.45250000000000001</v>
       </c>
-      <c r="E25">
-        <v>1E-4</v>
-      </c>
-      <c r="F25">
+      <c r="E29">
+        <v>1E-4</v>
+      </c>
+      <c r="F29" s="3">
+        <v>548.21</v>
+      </c>
+      <c r="G29">
         <v>548</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="E26">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F26">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27">
-        <v>0.53100000000000003</v>
-      </c>
-      <c r="E27">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="F27">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28">
-        <v>0.54220000000000002</v>
-      </c>
-      <c r="E28">
-        <v>2.9999999999999997E-4</v>
-      </c>
-      <c r="F28">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29">
-        <v>0.55300000000000005</v>
-      </c>
-      <c r="E29">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="F29">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D30">
-        <v>0.62139999999999995</v>
+        <v>3.6799999999999999E-2</v>
       </c>
       <c r="E30">
         <v>1E-4</v>
       </c>
-      <c r="F30">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F30" s="3">
+        <v>395.8</v>
+      </c>
+      <c r="G30">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D31">
-        <v>0.97499999999999998</v>
+        <v>0.2621</v>
       </c>
       <c r="E31">
-        <v>5.9999999999999995E-4</v>
-      </c>
-      <c r="F31">
-        <v>1347</v>
+        <v>1E-4</v>
+      </c>
+      <c r="F31" s="3">
+        <v>356.1</v>
+      </c>
+      <c r="G31">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F31">
+    <sortCondition ref="A9:A31"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>